--- a/flare-pwr/Examples/CaseLBLOCA_cold_in.xlsx
+++ b/flare-pwr/Examples/CaseLBLOCA_cold_in.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b11560d98c47b3/Documents/Current Work Activities/FLASH Model/Integrated Model/flare-pwr/Examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="11_6347EE8A944C94BE6D09D0D64E5DCE3AD7408283" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFBF6888-F2BF-42D6-BA12-0709A4FEEE50}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="11_6347EE8A944C94BE6D09D0D64E5DCE3AD7408283" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97634FDE-AEB6-4188-80E9-D4CE85BF2A40}"/>
   <bookViews>
-    <workbookView xWindow="3990" yWindow="1695" windowWidth="15180" windowHeight="9150" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="525" yWindow="1440" windowWidth="15840" windowHeight="9150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CaseLBLOCA_cold_in" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="251">
   <si>
     <t># CaseLBLOCA_cold_in
 # Cold-leg double-ended guillotine break (0.20 m). Full core model + DNBR.
@@ -31,9 +31,6 @@
     <t># Job Control</t>
   </si>
   <si>
-    <t>endtime = 800    # captures depressurisation, uncovery, and reflood [s]</t>
-  </si>
-  <si>
     <t># RCS Geometry</t>
   </si>
   <si>
@@ -199,9 +196,6 @@
     <t>T_fuel_limit_C = 1500    # fuel failure threshold [°C]</t>
   </si>
   <si>
-    <t>htc_post_chf = 450    # Bromley HTC cap [W/m²K]</t>
-  </si>
-  <si>
     <t>post_chf_model = "cold_leg"    # post-CHF model</t>
   </si>
   <si>
@@ -388,12 +382,6 @@
     <t xml:space="preserve">   nbt_credit_deposition = False</t>
   </si>
   <si>
-    <t>break_elevation_m =  7.0         # Cold leg break location</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> dry_core_trigger_level_m = 4.0</t>
-  </si>
-  <si>
     <t>Hold value</t>
   </si>
   <si>
@@ -779,6 +767,15 @@
   </si>
   <si>
     <t>PWR Dry Containment Response Simulator — Input File</t>
+  </si>
+  <si>
+    <t># break_elevation_m =  7.0         # Cold leg break location</t>
+  </si>
+  <si>
+    <t>dry_core_trigger_level_m = 4.0</t>
+  </si>
+  <si>
+    <t>endtime = 1200    # captures depressurisation, uncovery, and reflood [s]</t>
   </si>
 </sst>
 </file>
@@ -1255,7 +1252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J306"/>
+  <dimension ref="A1:J305"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="66" customWidth="1"/>
@@ -1267,7 +1264,7 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" ht="24" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B1" s="2"/>
     </row>
@@ -1289,45 +1286,45 @@
     </row>
     <row r="5" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>2</v>
+        <v>250</v>
       </c>
       <c r="B5" s="3"/>
     </row>
     <row r="6" spans="1:2" s="1" customFormat="1" ht="5.0999999999999996" customHeight="1"/>
     <row r="7" spans="1:2" s="1" customFormat="1" ht="15.95" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="2"/>
     </row>
     <row r="8" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="2"/>
     </row>
     <row r="11" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:2" s="1" customFormat="1" ht="5.0999999999999996" customHeight="1">
@@ -1336,33 +1333,33 @@
     </row>
     <row r="13" spans="1:2" s="1" customFormat="1" ht="15.95" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2"/>
     </row>
@@ -1372,75 +1369,75 @@
     </row>
     <row r="19" spans="1:2" s="1" customFormat="1" ht="15.95" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19" s="2"/>
     </row>
     <row r="20" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" s="3"/>
     </row>
     <row r="21" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" s="5"/>
     </row>
     <row r="22" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" s="3"/>
     </row>
     <row r="23" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="3"/>
     </row>
     <row r="25" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="5"/>
     </row>
     <row r="26" spans="1:2" s="1" customFormat="1" ht="5.0999999999999996" customHeight="1"/>
     <row r="27" spans="1:2" s="1" customFormat="1" ht="15.95" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27" s="4"/>
     </row>
     <row r="28" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="4"/>
     </row>
     <row r="30" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:2" s="1" customFormat="1" ht="5.0999999999999996" customHeight="1">
@@ -1449,45 +1446,45 @@
     </row>
     <row r="32" spans="1:2" s="1" customFormat="1" ht="15.95" customHeight="1">
       <c r="A32" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="4"/>
     </row>
     <row r="33" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" s="4"/>
     </row>
     <row r="35" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35" s="4"/>
     </row>
     <row r="36" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A36" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" s="4"/>
     </row>
     <row r="37" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37" s="4"/>
     </row>
     <row r="38" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A38" s="4" t="s">
-        <v>121</v>
+        <v>248</v>
       </c>
       <c r="B38" s="4"/>
     </row>
@@ -1497,65 +1494,65 @@
     </row>
     <row r="40" spans="1:2" s="1" customFormat="1" ht="15.95" customHeight="1">
       <c r="A40" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B40" s="4"/>
     </row>
     <row r="41" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A41" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A42" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B43" s="4"/>
     </row>
     <row r="44" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B44" s="4"/>
     </row>
     <row r="45" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B45" s="4"/>
     </row>
     <row r="46" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A46" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B46" s="4"/>
     </row>
     <row r="47" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" s="4"/>
     </row>
     <row r="48" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A48" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B48" s="4"/>
     </row>
     <row r="49" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49" s="4"/>
     </row>
@@ -1565,25 +1562,25 @@
     </row>
     <row r="51" spans="1:2" s="1" customFormat="1" ht="15.95" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B51" s="4"/>
     </row>
     <row r="52" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A52" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B52" s="4"/>
     </row>
     <row r="53" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A53" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B53" s="4"/>
     </row>
     <row r="54" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A54" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B54" s="4"/>
     </row>
@@ -1593,24 +1590,24 @@
     </row>
     <row r="56" spans="1:2" s="1" customFormat="1" ht="15.95" customHeight="1">
       <c r="A56" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B56" s="4"/>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="58" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A58" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B58" s="4"/>
     </row>
     <row r="59" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A59" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B59" s="4"/>
     </row>
@@ -1620,21 +1617,23 @@
     </row>
     <row r="61" spans="1:2" s="1" customFormat="1" ht="15.95" customHeight="1">
       <c r="A61" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B61" s="4"/>
     </row>
     <row r="62" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A62" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B62" s="4"/>
     </row>
     <row r="63" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A63" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B63" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B63" s="4"/>
     </row>
     <row r="64" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A64" s="4" t="s">
@@ -1648,128 +1647,131 @@
       <c r="A65" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B65" s="4" t="s">
-        <v>62</v>
-      </c>
+      <c r="B65" s="4"/>
     </row>
     <row r="66" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A66" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B66" s="4"/>
     </row>
     <row r="67" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A67" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B67" s="4"/>
     </row>
     <row r="68" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A68" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" s="1" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A69" s="4"/>
+      <c r="B69" s="4"/>
+    </row>
+    <row r="70" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1">
+      <c r="A70" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B70" s="4"/>
+    </row>
+    <row r="71" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A71" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="B68" s="4"/>
-    </row>
-    <row r="69" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A69" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" s="1" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A70" s="4"/>
-      <c r="B70" s="4"/>
-    </row>
-    <row r="71" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A71" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="B71" s="4"/>
     </row>
     <row r="72" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A72" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B72" s="4"/>
     </row>
     <row r="73" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A73" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B73" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B73" s="4"/>
-    </row>
-    <row r="74" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A74" s="4" t="s">
+    </row>
+    <row r="74" spans="1:7" s="1" customFormat="1" ht="11.25" customHeight="1">
+      <c r="A74" s="4"/>
+      <c r="B74" s="4"/>
+    </row>
+    <row r="75" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1">
+      <c r="A75" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B75" s="4"/>
+    </row>
+    <row r="76" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1">
+      <c r="A76" t="s">
+        <v>107</v>
+      </c>
+      <c r="B76" s="4"/>
+      <c r="F76" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" s="1" customFormat="1" ht="11.25" customHeight="1">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
-    </row>
-    <row r="76" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A76" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B76" s="4"/>
+      <c r="G76" s="4"/>
     </row>
     <row r="77" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A77" t="s">
-        <v>109</v>
+      <c r="A77" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="B77" s="4"/>
       <c r="F77" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G77" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G77" s="4"/>
     </row>
     <row r="78" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1">
       <c r="A78" s="4" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="B78" s="4"/>
       <c r="F78" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="G78" s="4" t="s">
-        <v>74</v>
-      </c>
+      <c r="G78" s="4"/>
     </row>
     <row r="79" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1">
       <c r="A79" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B79" s="4"/>
       <c r="F79" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G79" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="G79" s="4"/>
-    </row>
-    <row r="80" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1">
+    </row>
+    <row r="80" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A80" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B80" s="4"/>
+        <v>110</v>
+      </c>
       <c r="F80" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="G80" s="4" t="s">
-        <v>77</v>
-      </c>
+      <c r="G80" s="4"/>
     </row>
     <row r="81" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A81" s="4" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="F81" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G81" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="G81" s="4"/>
     </row>
     <row r="82" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A82" s="4" t="s">
@@ -1784,7 +1786,7 @@
     </row>
     <row r="83" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A83" s="4" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>81</v>
@@ -1795,7 +1797,7 @@
     </row>
     <row r="84" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A84" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>83</v>
@@ -1806,7 +1808,7 @@
     </row>
     <row r="85" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A85" s="4" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>85</v>
@@ -1817,63 +1819,63 @@
     </row>
     <row r="86" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A86" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="G86" s="4" t="s">
-        <v>88</v>
-      </c>
+      <c r="G86" s="4"/>
     </row>
     <row r="87" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A87" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G87" s="4"/>
     </row>
     <row r="88" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A88" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G88" s="4"/>
+    </row>
+    <row r="89" spans="1:7" s="1" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A89" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G89" s="4"/>
+    </row>
+    <row r="90" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A90" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F90" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="F88" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G88" s="4"/>
-    </row>
-    <row r="89" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A89" s="4" t="s">
+      <c r="G90" s="4"/>
+    </row>
+    <row r="91" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A91" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F89" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="G89" s="4"/>
-    </row>
-    <row r="90" spans="1:7" s="1" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A90" s="7" t="s">
+      <c r="F91" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A92" t="s">
         <v>115</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="G90" s="4"/>
-    </row>
-    <row r="91" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A91" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G91" s="4"/>
-    </row>
-    <row r="92" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A92" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>94</v>
@@ -1884,68 +1886,77 @@
     </row>
     <row r="93" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A93" t="s">
-        <v>117</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G93" s="4" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
     </row>
     <row r="94" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A94" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="95" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A95" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A96" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="98" spans="1:10" s="1" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A98" s="4"/>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="97" spans="1:10" s="1" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A97" s="4"/>
+      <c r="B97" s="4"/>
+    </row>
+    <row r="98" spans="1:10" s="1" customFormat="1" ht="15.95" customHeight="1">
+      <c r="A98" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="B98" s="4"/>
     </row>
-    <row r="99" spans="1:10" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="99" spans="1:10" s="1" customFormat="1" ht="26.1" customHeight="1">
       <c r="A99" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B99" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B99" s="4"/>
-    </row>
-    <row r="100" spans="1:10" s="1" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A100" s="4" t="s">
+      <c r="C99" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="D99" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="E99" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D100" s="4" t="s">
+      <c r="F99" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E100" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="G100" s="4"/>
-      <c r="H100" s="4"/>
-      <c r="I100" s="4"/>
-      <c r="J100" s="4"/>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
+    </row>
+    <row r="100" spans="1:10" s="1" customFormat="1" ht="14.1" customHeight="1">
+      <c r="A100" s="6">
+        <v>0</v>
+      </c>
+      <c r="B100" s="6">
+        <v>0</v>
+      </c>
+      <c r="C100" s="6">
+        <v>0</v>
+      </c>
+      <c r="D100" s="6">
+        <v>0</v>
+      </c>
+      <c r="E100" s="6">
+        <v>0</v>
+      </c>
+      <c r="F100" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="101" spans="1:10" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A101" s="6">
-        <v>0</v>
+        <v>0.50189850000000003</v>
       </c>
       <c r="B101" s="6">
         <v>0</v>
@@ -1965,7 +1976,7 @@
     </row>
     <row r="102" spans="1:10" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A102" s="6">
-        <v>0.50189850000000003</v>
+        <v>1.0018990000000001</v>
       </c>
       <c r="B102" s="6">
         <v>0</v>
@@ -1985,7 +1996,7 @@
     </row>
     <row r="103" spans="1:10" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A103" s="6">
-        <v>1.0018990000000001</v>
+        <v>1.5018990000000001</v>
       </c>
       <c r="B103" s="6">
         <v>0</v>
@@ -2005,7 +2016,7 @@
     </row>
     <row r="104" spans="1:10" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A104" s="6">
-        <v>1.5018990000000001</v>
+        <v>2.0018989999999999</v>
       </c>
       <c r="B104" s="6">
         <v>0</v>
@@ -2025,7 +2036,7 @@
     </row>
     <row r="105" spans="1:10" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A105" s="6">
-        <v>2.0018989999999999</v>
+        <v>2.5018989999999999</v>
       </c>
       <c r="B105" s="6">
         <v>0</v>
@@ -2045,7 +2056,7 @@
     </row>
     <row r="106" spans="1:10" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A106" s="6">
-        <v>2.5018989999999999</v>
+        <v>3.0018989999999999</v>
       </c>
       <c r="B106" s="6">
         <v>0</v>
@@ -2065,7 +2076,7 @@
     </row>
     <row r="107" spans="1:10" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A107" s="6">
-        <v>3.0018989999999999</v>
+        <v>3.5018989999999999</v>
       </c>
       <c r="B107" s="6">
         <v>0</v>
@@ -2085,7 +2096,7 @@
     </row>
     <row r="108" spans="1:10" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A108" s="6">
-        <v>3.5018989999999999</v>
+        <v>4.0018979999999997</v>
       </c>
       <c r="B108" s="6">
         <v>0</v>
@@ -2105,7 +2116,7 @@
     </row>
     <row r="109" spans="1:10" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A109" s="6">
-        <v>4.0018979999999997</v>
+        <v>4.5018979999999997</v>
       </c>
       <c r="B109" s="6">
         <v>0</v>
@@ -2125,7 +2136,7 @@
     </row>
     <row r="110" spans="1:10" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A110" s="6">
-        <v>4.5018979999999997</v>
+        <v>5.0018979999999997</v>
       </c>
       <c r="B110" s="6">
         <v>0</v>
@@ -2145,7 +2156,7 @@
     </row>
     <row r="111" spans="1:10" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A111" s="6">
-        <v>5.0018979999999997</v>
+        <v>5.5018979999999997</v>
       </c>
       <c r="B111" s="6">
         <v>0</v>
@@ -2165,7 +2176,7 @@
     </row>
     <row r="112" spans="1:10" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A112" s="6">
-        <v>5.5018979999999997</v>
+        <v>6.0018979999999997</v>
       </c>
       <c r="B112" s="6">
         <v>0</v>
@@ -2185,7 +2196,7 @@
     </row>
     <row r="113" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A113" s="6">
-        <v>6.0018979999999997</v>
+        <v>6.5018979999999997</v>
       </c>
       <c r="B113" s="6">
         <v>0</v>
@@ -2205,7 +2216,7 @@
     </row>
     <row r="114" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A114" s="6">
-        <v>6.5018979999999997</v>
+        <v>7.0018979999999997</v>
       </c>
       <c r="B114" s="6">
         <v>0</v>
@@ -2225,7 +2236,7 @@
     </row>
     <row r="115" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A115" s="6">
-        <v>7.0018979999999997</v>
+        <v>7.5018979999999997</v>
       </c>
       <c r="B115" s="6">
         <v>0</v>
@@ -2245,7 +2256,7 @@
     </row>
     <row r="116" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A116" s="6">
-        <v>7.5018979999999997</v>
+        <v>8.0018989999999999</v>
       </c>
       <c r="B116" s="6">
         <v>0</v>
@@ -2265,7 +2276,7 @@
     </row>
     <row r="117" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A117" s="6">
-        <v>8.0018989999999999</v>
+        <v>8.5018989999999999</v>
       </c>
       <c r="B117" s="6">
         <v>0</v>
@@ -2285,7 +2296,7 @@
     </row>
     <row r="118" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A118" s="6">
-        <v>8.5018989999999999</v>
+        <v>9.0018989999999999</v>
       </c>
       <c r="B118" s="6">
         <v>0</v>
@@ -2305,7 +2316,7 @@
     </row>
     <row r="119" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A119" s="6">
-        <v>9.0018989999999999</v>
+        <v>9.5018989999999999</v>
       </c>
       <c r="B119" s="6">
         <v>0</v>
@@ -2325,7 +2336,7 @@
     </row>
     <row r="120" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A120" s="6">
-        <v>9.5018989999999999</v>
+        <v>10.001899999999999</v>
       </c>
       <c r="B120" s="6">
         <v>0</v>
@@ -2345,7 +2356,7 @@
     </row>
     <row r="121" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A121" s="6">
-        <v>10.001899999999999</v>
+        <v>10.501899999999999</v>
       </c>
       <c r="B121" s="6">
         <v>0</v>
@@ -2365,7 +2376,7 @@
     </row>
     <row r="122" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A122" s="6">
-        <v>10.501899999999999</v>
+        <v>11.001899999999999</v>
       </c>
       <c r="B122" s="6">
         <v>0</v>
@@ -2385,7 +2396,7 @@
     </row>
     <row r="123" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A123" s="6">
-        <v>11.001899999999999</v>
+        <v>11.501899999999999</v>
       </c>
       <c r="B123" s="6">
         <v>0</v>
@@ -2405,7 +2416,7 @@
     </row>
     <row r="124" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A124" s="6">
-        <v>11.501899999999999</v>
+        <v>12.001899999999999</v>
       </c>
       <c r="B124" s="6">
         <v>0</v>
@@ -2425,7 +2436,7 @@
     </row>
     <row r="125" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A125" s="6">
-        <v>12.001899999999999</v>
+        <v>12.501899999999999</v>
       </c>
       <c r="B125" s="6">
         <v>0</v>
@@ -2445,7 +2456,7 @@
     </row>
     <row r="126" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A126" s="6">
-        <v>12.501899999999999</v>
+        <v>13.001899999999999</v>
       </c>
       <c r="B126" s="6">
         <v>0</v>
@@ -2465,7 +2476,7 @@
     </row>
     <row r="127" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A127" s="6">
-        <v>13.001899999999999</v>
+        <v>13.501899999999999</v>
       </c>
       <c r="B127" s="6">
         <v>0</v>
@@ -2485,7 +2496,7 @@
     </row>
     <row r="128" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A128" s="6">
-        <v>13.501899999999999</v>
+        <v>14.001899999999999</v>
       </c>
       <c r="B128" s="6">
         <v>0</v>
@@ -2505,7 +2516,7 @@
     </row>
     <row r="129" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A129" s="6">
-        <v>14.001899999999999</v>
+        <v>14.501899999999999</v>
       </c>
       <c r="B129" s="6">
         <v>0</v>
@@ -2525,7 +2536,7 @@
     </row>
     <row r="130" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A130" s="6">
-        <v>14.501899999999999</v>
+        <v>15.0009</v>
       </c>
       <c r="B130" s="6">
         <v>0</v>
@@ -2545,7 +2556,7 @@
     </row>
     <row r="131" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A131" s="6">
-        <v>15.0009</v>
+        <v>16.001449999999998</v>
       </c>
       <c r="B131" s="6">
         <v>0</v>
@@ -2565,7 +2576,7 @@
     </row>
     <row r="132" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A132" s="6">
-        <v>16.001449999999998</v>
+        <v>17.00123</v>
       </c>
       <c r="B132" s="6">
         <v>0</v>
@@ -2585,7 +2596,7 @@
     </row>
     <row r="133" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A133" s="6">
-        <v>17.00123</v>
+        <v>18.001429999999999</v>
       </c>
       <c r="B133" s="6">
         <v>0</v>
@@ -2605,7 +2616,7 @@
     </row>
     <row r="134" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A134" s="6">
-        <v>18.001429999999999</v>
+        <v>19.002050000000001</v>
       </c>
       <c r="B134" s="6">
         <v>0</v>
@@ -2625,7 +2636,7 @@
     </row>
     <row r="135" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A135" s="6">
-        <v>19.002050000000001</v>
+        <v>20.001339999999999</v>
       </c>
       <c r="B135" s="6">
         <v>0</v>
@@ -2645,7 +2656,7 @@
     </row>
     <row r="136" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A136" s="6">
-        <v>20.001339999999999</v>
+        <v>21.00207</v>
       </c>
       <c r="B136" s="6">
         <v>0</v>
@@ -2665,7 +2676,7 @@
     </row>
     <row r="137" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A137" s="6">
-        <v>21.00207</v>
+        <v>22.001460000000002</v>
       </c>
       <c r="B137" s="6">
         <v>0</v>
@@ -2685,7 +2696,7 @@
     </row>
     <row r="138" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A138" s="6">
-        <v>22.001460000000002</v>
+        <v>23.001750000000001</v>
       </c>
       <c r="B138" s="6">
         <v>0</v>
@@ -2705,7 +2716,7 @@
     </row>
     <row r="139" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A139" s="6">
-        <v>23.001750000000001</v>
+        <v>24.002279999999999</v>
       </c>
       <c r="B139" s="6">
         <v>0</v>
@@ -2725,7 +2736,7 @@
     </row>
     <row r="140" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A140" s="6">
-        <v>24.002279999999999</v>
+        <v>25.002549999999999</v>
       </c>
       <c r="B140" s="6">
         <v>0</v>
@@ -2745,7 +2756,7 @@
     </row>
     <row r="141" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A141" s="6">
-        <v>25.002549999999999</v>
+        <v>26.001860000000001</v>
       </c>
       <c r="B141" s="6">
         <v>0</v>
@@ -2765,7 +2776,7 @@
     </row>
     <row r="142" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A142" s="6">
-        <v>26.001860000000001</v>
+        <v>27.002220000000001</v>
       </c>
       <c r="B142" s="6">
         <v>0</v>
@@ -2785,7 +2796,7 @@
     </row>
     <row r="143" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A143" s="6">
-        <v>27.002220000000001</v>
+        <v>28.001290000000001</v>
       </c>
       <c r="B143" s="6">
         <v>0</v>
@@ -2805,7 +2816,7 @@
     </row>
     <row r="144" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A144" s="6">
-        <v>28.001290000000001</v>
+        <v>29.00226</v>
       </c>
       <c r="B144" s="6">
         <v>0</v>
@@ -2825,7 +2836,7 @@
     </row>
     <row r="145" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A145" s="6">
-        <v>29.00226</v>
+        <v>30.00151</v>
       </c>
       <c r="B145" s="6">
         <v>0</v>
@@ -2845,7 +2856,7 @@
     </row>
     <row r="146" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A146" s="6">
-        <v>30.00151</v>
+        <v>31.002330000000001</v>
       </c>
       <c r="B146" s="6">
         <v>0</v>
@@ -2865,7 +2876,7 @@
     </row>
     <row r="147" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A147" s="6">
-        <v>31.002330000000001</v>
+        <v>32.002200000000002</v>
       </c>
       <c r="B147" s="6">
         <v>0</v>
@@ -2885,7 +2896,7 @@
     </row>
     <row r="148" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A148" s="6">
-        <v>32.002200000000002</v>
+        <v>33.001280000000001</v>
       </c>
       <c r="B148" s="6">
         <v>0</v>
@@ -2905,7 +2916,7 @@
     </row>
     <row r="149" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A149" s="6">
-        <v>33.001280000000001</v>
+        <v>34.001510000000003</v>
       </c>
       <c r="B149" s="6">
         <v>0</v>
@@ -2925,7 +2936,7 @@
     </row>
     <row r="150" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A150" s="6">
-        <v>34.001510000000003</v>
+        <v>35.002409999999998</v>
       </c>
       <c r="B150" s="6">
         <v>0</v>
@@ -2945,7 +2956,7 @@
     </row>
     <row r="151" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A151" s="6">
-        <v>35.002409999999998</v>
+        <v>36.001139999999999</v>
       </c>
       <c r="B151" s="6">
         <v>0</v>
@@ -2965,7 +2976,7 @@
     </row>
     <row r="152" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A152" s="6">
-        <v>36.001139999999999</v>
+        <v>37.001289999999997</v>
       </c>
       <c r="B152" s="6">
         <v>0</v>
@@ -2985,7 +2996,7 @@
     </row>
     <row r="153" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A153" s="6">
-        <v>37.001289999999997</v>
+        <v>38.001910000000002</v>
       </c>
       <c r="B153" s="6">
         <v>0</v>
@@ -3005,7 +3016,7 @@
     </row>
     <row r="154" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A154" s="6">
-        <v>38.001910000000002</v>
+        <v>39.00264</v>
       </c>
       <c r="B154" s="6">
         <v>0</v>
@@ -3025,7 +3036,7 @@
     </row>
     <row r="155" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A155" s="6">
-        <v>39.00264</v>
+        <v>40.002310000000001</v>
       </c>
       <c r="B155" s="6">
         <v>0</v>
@@ -3045,7 +3056,7 @@
     </row>
     <row r="156" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A156" s="6">
-        <v>40.002310000000001</v>
+        <v>41.002189999999999</v>
       </c>
       <c r="B156" s="6">
         <v>0</v>
@@ -3065,7 +3076,7 @@
     </row>
     <row r="157" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A157" s="6">
-        <v>41.002189999999999</v>
+        <v>42.002339999999997</v>
       </c>
       <c r="B157" s="6">
         <v>0</v>
@@ -3085,7 +3096,7 @@
     </row>
     <row r="158" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A158" s="6">
-        <v>42.002339999999997</v>
+        <v>43.001480000000001</v>
       </c>
       <c r="B158" s="6">
         <v>0</v>
@@ -3105,7 +3116,7 @@
     </row>
     <row r="159" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A159" s="6">
-        <v>43.001480000000001</v>
+        <v>44.000900000000001</v>
       </c>
       <c r="B159" s="6">
         <v>0</v>
@@ -3125,7 +3136,7 @@
     </row>
     <row r="160" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A160" s="6">
-        <v>44.000900000000001</v>
+        <v>45.000900000000001</v>
       </c>
       <c r="B160" s="6">
         <v>0</v>
@@ -3145,7 +3156,7 @@
     </row>
     <row r="161" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A161" s="6">
-        <v>45.000900000000001</v>
+        <v>46.003019999999999</v>
       </c>
       <c r="B161" s="6">
         <v>0</v>
@@ -3165,7 +3176,7 @@
     </row>
     <row r="162" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A162" s="6">
-        <v>46.003019999999999</v>
+        <v>47.001150000000003</v>
       </c>
       <c r="B162" s="6">
         <v>0</v>
@@ -3185,7 +3196,7 @@
     </row>
     <row r="163" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A163" s="6">
-        <v>47.001150000000003</v>
+        <v>48.001060000000003</v>
       </c>
       <c r="B163" s="6">
         <v>0</v>
@@ -3205,7 +3216,7 @@
     </row>
     <row r="164" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A164" s="6">
-        <v>48.001060000000003</v>
+        <v>49.001530000000002</v>
       </c>
       <c r="B164" s="6">
         <v>0</v>
@@ -3225,7 +3236,7 @@
     </row>
     <row r="165" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A165" s="6">
-        <v>49.001530000000002</v>
+        <v>50.00215</v>
       </c>
       <c r="B165" s="6">
         <v>0</v>
@@ -3245,7 +3256,7 @@
     </row>
     <row r="166" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A166" s="6">
-        <v>50.00215</v>
+        <v>51.002270000000003</v>
       </c>
       <c r="B166" s="6">
         <v>0</v>
@@ -3265,7 +3276,7 @@
     </row>
     <row r="167" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A167" s="6">
-        <v>51.002270000000003</v>
+        <v>52.002360000000003</v>
       </c>
       <c r="B167" s="6">
         <v>0</v>
@@ -3285,7 +3296,7 @@
     </row>
     <row r="168" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A168" s="6">
-        <v>52.002360000000003</v>
+        <v>53.001339999999999</v>
       </c>
       <c r="B168" s="6">
         <v>0</v>
@@ -3305,7 +3316,7 @@
     </row>
     <row r="169" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A169" s="6">
-        <v>53.001339999999999</v>
+        <v>54.002800000000001</v>
       </c>
       <c r="B169" s="6">
         <v>0</v>
@@ -3325,7 +3336,7 @@
     </row>
     <row r="170" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A170" s="6">
-        <v>54.002800000000001</v>
+        <v>55.001890000000003</v>
       </c>
       <c r="B170" s="6">
         <v>0</v>
@@ -3345,7 +3356,7 @@
     </row>
     <row r="171" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A171" s="6">
-        <v>55.001890000000003</v>
+        <v>56.002189999999999</v>
       </c>
       <c r="B171" s="6">
         <v>0</v>
@@ -3365,7 +3376,7 @@
     </row>
     <row r="172" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A172" s="6">
-        <v>56.002189999999999</v>
+        <v>57.002589999999998</v>
       </c>
       <c r="B172" s="6">
         <v>0</v>
@@ -3385,7 +3396,7 @@
     </row>
     <row r="173" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A173" s="6">
-        <v>57.002589999999998</v>
+        <v>58.002719999999997</v>
       </c>
       <c r="B173" s="6">
         <v>0</v>
@@ -3405,7 +3416,7 @@
     </row>
     <row r="174" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A174" s="6">
-        <v>58.002719999999997</v>
+        <v>59.00132</v>
       </c>
       <c r="B174" s="6">
         <v>0</v>
@@ -3425,7 +3436,7 @@
     </row>
     <row r="175" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A175" s="6">
-        <v>59.00132</v>
+        <v>60.002429999999997</v>
       </c>
       <c r="B175" s="6">
         <v>0</v>
@@ -3445,7 +3456,7 @@
     </row>
     <row r="176" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A176" s="6">
-        <v>60.002429999999997</v>
+        <v>61.003120000000003</v>
       </c>
       <c r="B176" s="6">
         <v>0</v>
@@ -3465,7 +3476,7 @@
     </row>
     <row r="177" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A177" s="6">
-        <v>61.003120000000003</v>
+        <v>62.002960000000002</v>
       </c>
       <c r="B177" s="6">
         <v>0</v>
@@ -3485,7 +3496,7 @@
     </row>
     <row r="178" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A178" s="6">
-        <v>62.002960000000002</v>
+        <v>63.00141</v>
       </c>
       <c r="B178" s="6">
         <v>0</v>
@@ -3505,7 +3516,7 @@
     </row>
     <row r="179" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A179" s="6">
-        <v>63.00141</v>
+        <v>64.001249999999999</v>
       </c>
       <c r="B179" s="6">
         <v>0</v>
@@ -3525,7 +3536,7 @@
     </row>
     <row r="180" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A180" s="6">
-        <v>64.001249999999999</v>
+        <v>65.001559999999998</v>
       </c>
       <c r="B180" s="6">
         <v>0</v>
@@ -3545,7 +3556,7 @@
     </row>
     <row r="181" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A181" s="6">
-        <v>65.001559999999998</v>
+        <v>66.001350000000002</v>
       </c>
       <c r="B181" s="6">
         <v>0</v>
@@ -3565,7 +3576,7 @@
     </row>
     <row r="182" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A182" s="6">
-        <v>66.001350000000002</v>
+        <v>67.001750000000001</v>
       </c>
       <c r="B182" s="6">
         <v>0</v>
@@ -3585,7 +3596,7 @@
     </row>
     <row r="183" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A183" s="6">
-        <v>67.001750000000001</v>
+        <v>68.00215</v>
       </c>
       <c r="B183" s="6">
         <v>0</v>
@@ -3605,7 +3616,7 @@
     </row>
     <row r="184" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A184" s="6">
-        <v>68.00215</v>
+        <v>69.002030000000005</v>
       </c>
       <c r="B184" s="6">
         <v>0</v>
@@ -3625,7 +3636,7 @@
     </row>
     <row r="185" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A185" s="6">
-        <v>69.002030000000005</v>
+        <v>70.00179</v>
       </c>
       <c r="B185" s="6">
         <v>0</v>
@@ -3645,7 +3656,7 @@
     </row>
     <row r="186" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A186" s="6">
-        <v>70.00179</v>
+        <v>71.001850000000005</v>
       </c>
       <c r="B186" s="6">
         <v>0</v>
@@ -3665,7 +3676,7 @@
     </row>
     <row r="187" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A187" s="6">
-        <v>71.001850000000005</v>
+        <v>72.002319999999997</v>
       </c>
       <c r="B187" s="6">
         <v>0</v>
@@ -3685,7 +3696,7 @@
     </row>
     <row r="188" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A188" s="6">
-        <v>72.002319999999997</v>
+        <v>73.001509999999996</v>
       </c>
       <c r="B188" s="6">
         <v>0</v>
@@ -3705,7 +3716,7 @@
     </row>
     <row r="189" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A189" s="6">
-        <v>73.001509999999996</v>
+        <v>74.002219999999994</v>
       </c>
       <c r="B189" s="6">
         <v>0</v>
@@ -3725,7 +3736,7 @@
     </row>
     <row r="190" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A190" s="6">
-        <v>74.002219999999994</v>
+        <v>75.001559999999998</v>
       </c>
       <c r="B190" s="6">
         <v>0</v>
@@ -3745,7 +3756,7 @@
     </row>
     <row r="191" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A191" s="6">
-        <v>75.001559999999998</v>
+        <v>76.001050000000006</v>
       </c>
       <c r="B191" s="6">
         <v>0</v>
@@ -3765,7 +3776,7 @@
     </row>
     <row r="192" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A192" s="6">
-        <v>76.001050000000006</v>
+        <v>77.002170000000007</v>
       </c>
       <c r="B192" s="6">
         <v>0</v>
@@ -3785,7 +3796,7 @@
     </row>
     <row r="193" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A193" s="6">
-        <v>77.002170000000007</v>
+        <v>78.002430000000004</v>
       </c>
       <c r="B193" s="6">
         <v>0</v>
@@ -3805,7 +3816,7 @@
     </row>
     <row r="194" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A194" s="6">
-        <v>78.002430000000004</v>
+        <v>79.002489999999995</v>
       </c>
       <c r="B194" s="6">
         <v>0</v>
@@ -3825,7 +3836,7 @@
     </row>
     <row r="195" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A195" s="6">
-        <v>79.002489999999995</v>
+        <v>80.001570000000001</v>
       </c>
       <c r="B195" s="6">
         <v>0</v>
@@ -3845,7 +3856,7 @@
     </row>
     <row r="196" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A196" s="6">
-        <v>80.001570000000001</v>
+        <v>81.001429999999999</v>
       </c>
       <c r="B196" s="6">
         <v>0</v>
@@ -3865,7 +3876,7 @@
     </row>
     <row r="197" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A197" s="6">
-        <v>81.001429999999999</v>
+        <v>82.002300000000005</v>
       </c>
       <c r="B197" s="6">
         <v>0</v>
@@ -3885,7 +3896,7 @@
     </row>
     <row r="198" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A198" s="6">
-        <v>82.002300000000005</v>
+        <v>83.001649999999998</v>
       </c>
       <c r="B198" s="6">
         <v>0</v>
@@ -3905,7 +3916,7 @@
     </row>
     <row r="199" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A199" s="6">
-        <v>83.001649999999998</v>
+        <v>84.001949999999994</v>
       </c>
       <c r="B199" s="6">
         <v>0</v>
@@ -3925,7 +3936,7 @@
     </row>
     <row r="200" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A200" s="6">
-        <v>84.001949999999994</v>
+        <v>85.002120000000005</v>
       </c>
       <c r="B200" s="6">
         <v>0</v>
@@ -3945,7 +3956,7 @@
     </row>
     <row r="201" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A201" s="6">
-        <v>85.002120000000005</v>
+        <v>86.000979999999998</v>
       </c>
       <c r="B201" s="6">
         <v>0</v>
@@ -3965,7 +3976,7 @@
     </row>
     <row r="202" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A202" s="6">
-        <v>86.000979999999998</v>
+        <v>87.001890000000003</v>
       </c>
       <c r="B202" s="6">
         <v>0</v>
@@ -3985,7 +3996,7 @@
     </row>
     <row r="203" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A203" s="6">
-        <v>87.001890000000003</v>
+        <v>88.001289999999997</v>
       </c>
       <c r="B203" s="6">
         <v>0</v>
@@ -4005,7 +4016,7 @@
     </row>
     <row r="204" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A204" s="6">
-        <v>88.001289999999997</v>
+        <v>89.001540000000006</v>
       </c>
       <c r="B204" s="6">
         <v>0</v>
@@ -4025,7 +4036,7 @@
     </row>
     <row r="205" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A205" s="6">
-        <v>89.001540000000006</v>
+        <v>90.001869999999997</v>
       </c>
       <c r="B205" s="6">
         <v>0</v>
@@ -4045,7 +4056,7 @@
     </row>
     <row r="206" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A206" s="6">
-        <v>90.001869999999997</v>
+        <v>91.001440000000002</v>
       </c>
       <c r="B206" s="6">
         <v>0</v>
@@ -4065,7 +4076,7 @@
     </row>
     <row r="207" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A207" s="6">
-        <v>91.001440000000002</v>
+        <v>92.001040000000003</v>
       </c>
       <c r="B207" s="6">
         <v>0</v>
@@ -4085,7 +4096,7 @@
     </row>
     <row r="208" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A208" s="6">
-        <v>92.001040000000003</v>
+        <v>93.001400000000004</v>
       </c>
       <c r="B208" s="6">
         <v>0</v>
@@ -4105,7 +4116,7 @@
     </row>
     <row r="209" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A209" s="6">
-        <v>93.001400000000004</v>
+        <v>94.001310000000004</v>
       </c>
       <c r="B209" s="6">
         <v>0</v>
@@ -4125,7 +4136,7 @@
     </row>
     <row r="210" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A210" s="6">
-        <v>94.001310000000004</v>
+        <v>95.00197</v>
       </c>
       <c r="B210" s="6">
         <v>0</v>
@@ -4145,7 +4156,7 @@
     </row>
     <row r="211" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A211" s="6">
-        <v>95.00197</v>
+        <v>96.002009999999999</v>
       </c>
       <c r="B211" s="6">
         <v>0</v>
@@ -4165,7 +4176,7 @@
     </row>
     <row r="212" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A212" s="6">
-        <v>96.002009999999999</v>
+        <v>97.0017</v>
       </c>
       <c r="B212" s="6">
         <v>0</v>
@@ -4185,7 +4196,7 @@
     </row>
     <row r="213" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A213" s="6">
-        <v>97.0017</v>
+        <v>98.001540000000006</v>
       </c>
       <c r="B213" s="6">
         <v>0</v>
@@ -4205,7 +4216,7 @@
     </row>
     <row r="214" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A214" s="6">
-        <v>98.001540000000006</v>
+        <v>99.001850000000005</v>
       </c>
       <c r="B214" s="6">
         <v>0</v>
@@ -4225,7 +4236,7 @@
     </row>
     <row r="215" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A215" s="6">
-        <v>99.001850000000005</v>
+        <v>100.00109999999999</v>
       </c>
       <c r="B215" s="6">
         <v>0</v>
@@ -4245,7 +4256,7 @@
     </row>
     <row r="216" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A216" s="6">
-        <v>100.00109999999999</v>
+        <v>110.0013</v>
       </c>
       <c r="B216" s="6">
         <v>0</v>
@@ -4265,7 +4276,7 @@
     </row>
     <row r="217" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A217" s="6">
-        <v>110.0013</v>
+        <v>120.0018</v>
       </c>
       <c r="B217" s="6">
         <v>0</v>
@@ -4285,7 +4296,7 @@
     </row>
     <row r="218" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A218" s="6">
-        <v>120.0018</v>
+        <v>130.00210000000001</v>
       </c>
       <c r="B218" s="6">
         <v>0</v>
@@ -4305,7 +4316,7 @@
     </row>
     <row r="219" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A219" s="6">
-        <v>130.00210000000001</v>
+        <v>140.00139999999999</v>
       </c>
       <c r="B219" s="6">
         <v>0</v>
@@ -4325,7 +4336,7 @@
     </row>
     <row r="220" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A220" s="6">
-        <v>140.00139999999999</v>
+        <v>150.00190000000001</v>
       </c>
       <c r="B220" s="6">
         <v>0</v>
@@ -4345,7 +4356,7 @@
     </row>
     <row r="221" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A221" s="6">
-        <v>150.00190000000001</v>
+        <v>160.00219999999999</v>
       </c>
       <c r="B221" s="6">
         <v>0</v>
@@ -4365,7 +4376,7 @@
     </row>
     <row r="222" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A222" s="6">
-        <v>160.00219999999999</v>
+        <v>170.00219999999999</v>
       </c>
       <c r="B222" s="6">
         <v>0</v>
@@ -4385,7 +4396,7 @@
     </row>
     <row r="223" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A223" s="6">
-        <v>170.00219999999999</v>
+        <v>180.0017</v>
       </c>
       <c r="B223" s="6">
         <v>0</v>
@@ -4405,7 +4416,7 @@
     </row>
     <row r="224" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A224" s="6">
-        <v>180.0017</v>
+        <v>190.00190000000001</v>
       </c>
       <c r="B224" s="6">
         <v>0</v>
@@ -4425,7 +4436,7 @@
     </row>
     <row r="225" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A225" s="6">
-        <v>190.00190000000001</v>
+        <v>200.00190000000001</v>
       </c>
       <c r="B225" s="6">
         <v>0</v>
@@ -4445,7 +4456,7 @@
     </row>
     <row r="226" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A226" s="6">
-        <v>200.00190000000001</v>
+        <v>210.00120000000001</v>
       </c>
       <c r="B226" s="6">
         <v>0</v>
@@ -4465,7 +4476,7 @@
     </row>
     <row r="227" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A227" s="6">
-        <v>210.00120000000001</v>
+        <v>220.00120000000001</v>
       </c>
       <c r="B227" s="6">
         <v>0</v>
@@ -4485,7 +4496,7 @@
     </row>
     <row r="228" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A228" s="6">
-        <v>220.00120000000001</v>
+        <v>230.0017</v>
       </c>
       <c r="B228" s="6">
         <v>0</v>
@@ -4505,7 +4516,7 @@
     </row>
     <row r="229" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A229" s="6">
-        <v>230.0017</v>
+        <v>240.00200000000001</v>
       </c>
       <c r="B229" s="6">
         <v>0</v>
@@ -4525,7 +4536,7 @@
     </row>
     <row r="230" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A230" s="6">
-        <v>240.00200000000001</v>
+        <v>250.00129999999999</v>
       </c>
       <c r="B230" s="6">
         <v>0</v>
@@ -4545,7 +4556,7 @@
     </row>
     <row r="231" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A231" s="6">
-        <v>250.00129999999999</v>
+        <v>260.0018</v>
       </c>
       <c r="B231" s="6">
         <v>0</v>
@@ -4565,7 +4576,7 @@
     </row>
     <row r="232" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A232" s="6">
-        <v>260.0018</v>
+        <v>270.00119999999998</v>
       </c>
       <c r="B232" s="6">
         <v>0</v>
@@ -4585,7 +4596,7 @@
     </row>
     <row r="233" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A233" s="6">
-        <v>270.00119999999998</v>
+        <v>280.00170000000003</v>
       </c>
       <c r="B233" s="6">
         <v>0</v>
@@ -4605,7 +4616,7 @@
     </row>
     <row r="234" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A234" s="6">
-        <v>280.00170000000003</v>
+        <v>290.00150000000002</v>
       </c>
       <c r="B234" s="6">
         <v>0</v>
@@ -4625,7 +4636,7 @@
     </row>
     <row r="235" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A235" s="6">
-        <v>290.00150000000002</v>
+        <v>300.0016</v>
       </c>
       <c r="B235" s="6">
         <v>0</v>
@@ -4645,7 +4656,7 @@
     </row>
     <row r="236" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A236" s="6">
-        <v>300.0016</v>
+        <v>310.00189999999998</v>
       </c>
       <c r="B236" s="6">
         <v>0</v>
@@ -4665,7 +4676,7 @@
     </row>
     <row r="237" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A237" s="6">
-        <v>310.00189999999998</v>
+        <v>320.00170000000003</v>
       </c>
       <c r="B237" s="6">
         <v>0</v>
@@ -4685,7 +4696,7 @@
     </row>
     <row r="238" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A238" s="6">
-        <v>320.00170000000003</v>
+        <v>330.00150000000002</v>
       </c>
       <c r="B238" s="6">
         <v>0</v>
@@ -4705,7 +4716,7 @@
     </row>
     <row r="239" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A239" s="6">
-        <v>330.00150000000002</v>
+        <v>340.00189999999998</v>
       </c>
       <c r="B239" s="6">
         <v>0</v>
@@ -4725,7 +4736,7 @@
     </row>
     <row r="240" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A240" s="6">
-        <v>340.00189999999998</v>
+        <v>350.00170000000003</v>
       </c>
       <c r="B240" s="6">
         <v>0</v>
@@ -4745,7 +4756,7 @@
     </row>
     <row r="241" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A241" s="6">
-        <v>350.00170000000003</v>
+        <v>360.00150000000002</v>
       </c>
       <c r="B241" s="6">
         <v>0</v>
@@ -4765,7 +4776,7 @@
     </row>
     <row r="242" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A242" s="6">
-        <v>360.00150000000002</v>
+        <v>370.00150000000002</v>
       </c>
       <c r="B242" s="6">
         <v>0</v>
@@ -4785,7 +4796,7 @@
     </row>
     <row r="243" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A243" s="6">
-        <v>370.00150000000002</v>
+        <v>380.00139999999999</v>
       </c>
       <c r="B243" s="6">
         <v>0</v>
@@ -4805,7 +4816,7 @@
     </row>
     <row r="244" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A244" s="6">
-        <v>380.00139999999999</v>
+        <v>390.00200000000001</v>
       </c>
       <c r="B244" s="6">
         <v>0</v>
@@ -4825,7 +4836,7 @@
     </row>
     <row r="245" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A245" s="6">
-        <v>390.00200000000001</v>
+        <v>400.00200000000001</v>
       </c>
       <c r="B245" s="6">
         <v>0</v>
@@ -4845,7 +4856,7 @@
     </row>
     <row r="246" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A246" s="6">
-        <v>400.00200000000001</v>
+        <v>410.0016</v>
       </c>
       <c r="B246" s="6">
         <v>0</v>
@@ -4865,7 +4876,7 @@
     </row>
     <row r="247" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A247" s="6">
-        <v>410.0016</v>
+        <v>420.0016</v>
       </c>
       <c r="B247" s="6">
         <v>0</v>
@@ -4885,7 +4896,7 @@
     </row>
     <row r="248" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A248" s="6">
-        <v>420.0016</v>
+        <v>430.00200000000001</v>
       </c>
       <c r="B248" s="6">
         <v>0</v>
@@ -4905,7 +4916,7 @@
     </row>
     <row r="249" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A249" s="6">
-        <v>430.00200000000001</v>
+        <v>440.00189999999998</v>
       </c>
       <c r="B249" s="6">
         <v>0</v>
@@ -4925,7 +4936,7 @@
     </row>
     <row r="250" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A250" s="6">
-        <v>440.00189999999998</v>
+        <v>450.00170000000003</v>
       </c>
       <c r="B250" s="6">
         <v>0</v>
@@ -4945,7 +4956,7 @@
     </row>
     <row r="251" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A251" s="6">
-        <v>450.00170000000003</v>
+        <v>460.0018</v>
       </c>
       <c r="B251" s="6">
         <v>0</v>
@@ -4965,7 +4976,7 @@
     </row>
     <row r="252" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A252" s="6">
-        <v>460.0018</v>
+        <v>470.00130000000001</v>
       </c>
       <c r="B252" s="6">
         <v>0</v>
@@ -4985,7 +4996,7 @@
     </row>
     <row r="253" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A253" s="6">
-        <v>470.00130000000001</v>
+        <v>480.00150000000002</v>
       </c>
       <c r="B253" s="6">
         <v>0</v>
@@ -5005,7 +5016,7 @@
     </row>
     <row r="254" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A254" s="6">
-        <v>480.00150000000002</v>
+        <v>490.0016</v>
       </c>
       <c r="B254" s="6">
         <v>0</v>
@@ -5025,7 +5036,7 @@
     </row>
     <row r="255" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A255" s="6">
-        <v>490.0016</v>
+        <v>500.00200000000001</v>
       </c>
       <c r="B255" s="6">
         <v>0</v>
@@ -5045,7 +5056,7 @@
     </row>
     <row r="256" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A256" s="6">
-        <v>500.00200000000001</v>
+        <v>510.0025</v>
       </c>
       <c r="B256" s="6">
         <v>0</v>
@@ -5065,7 +5076,7 @@
     </row>
     <row r="257" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A257" s="6">
-        <v>510.0025</v>
+        <v>520.00199999999995</v>
       </c>
       <c r="B257" s="6">
         <v>0</v>
@@ -5085,7 +5096,7 @@
     </row>
     <row r="258" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A258" s="6">
-        <v>520.00199999999995</v>
+        <v>530.00139999999999</v>
       </c>
       <c r="B258" s="6">
         <v>0</v>
@@ -5105,7 +5116,7 @@
     </row>
     <row r="259" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A259" s="6">
-        <v>530.00139999999999</v>
+        <v>540.00210000000004</v>
       </c>
       <c r="B259" s="6">
         <v>0</v>
@@ -5125,7 +5136,7 @@
     </row>
     <row r="260" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A260" s="6">
-        <v>540.00210000000004</v>
+        <v>550.0018</v>
       </c>
       <c r="B260" s="6">
         <v>0</v>
@@ -5145,7 +5156,7 @@
     </row>
     <row r="261" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A261" s="6">
-        <v>550.0018</v>
+        <v>560.00220000000002</v>
       </c>
       <c r="B261" s="6">
         <v>0</v>
@@ -5165,7 +5176,7 @@
     </row>
     <row r="262" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A262" s="6">
-        <v>560.00220000000002</v>
+        <v>570.0018</v>
       </c>
       <c r="B262" s="6">
         <v>0</v>
@@ -5185,7 +5196,7 @@
     </row>
     <row r="263" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A263" s="6">
-        <v>570.0018</v>
+        <v>580.00220000000002</v>
       </c>
       <c r="B263" s="6">
         <v>0</v>
@@ -5205,7 +5216,7 @@
     </row>
     <row r="264" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A264" s="6">
-        <v>580.00220000000002</v>
+        <v>590.00130000000001</v>
       </c>
       <c r="B264" s="6">
         <v>0</v>
@@ -5225,7 +5236,7 @@
     </row>
     <row r="265" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A265" s="6">
-        <v>590.00130000000001</v>
+        <v>600.00120000000004</v>
       </c>
       <c r="B265" s="6">
         <v>0</v>
@@ -5245,7 +5256,7 @@
     </row>
     <row r="266" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A266" s="6">
-        <v>600.00120000000004</v>
+        <v>610.00120000000004</v>
       </c>
       <c r="B266" s="6">
         <v>0</v>
@@ -5265,7 +5276,7 @@
     </row>
     <row r="267" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A267" s="6">
-        <v>610.00120000000004</v>
+        <v>620.00130000000001</v>
       </c>
       <c r="B267" s="6">
         <v>0</v>
@@ -5285,7 +5296,7 @@
     </row>
     <row r="268" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A268" s="6">
-        <v>620.00130000000001</v>
+        <v>630.00160000000005</v>
       </c>
       <c r="B268" s="6">
         <v>0</v>
@@ -5305,7 +5316,7 @@
     </row>
     <row r="269" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A269" s="6">
-        <v>630.00160000000005</v>
+        <v>640.00239999999997</v>
       </c>
       <c r="B269" s="6">
         <v>0</v>
@@ -5325,7 +5336,7 @@
     </row>
     <row r="270" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A270" s="6">
-        <v>640.00239999999997</v>
+        <v>650.00229999999999</v>
       </c>
       <c r="B270" s="6">
         <v>0</v>
@@ -5345,7 +5356,7 @@
     </row>
     <row r="271" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A271" s="6">
-        <v>650.00229999999999</v>
+        <v>660.0018</v>
       </c>
       <c r="B271" s="6">
         <v>0</v>
@@ -5365,7 +5376,7 @@
     </row>
     <row r="272" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A272" s="6">
-        <v>660.0018</v>
+        <v>670.00250000000005</v>
       </c>
       <c r="B272" s="6">
         <v>0</v>
@@ -5385,7 +5396,7 @@
     </row>
     <row r="273" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A273" s="6">
-        <v>670.00250000000005</v>
+        <v>680.00120000000004</v>
       </c>
       <c r="B273" s="6">
         <v>0</v>
@@ -5405,7 +5416,7 @@
     </row>
     <row r="274" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A274" s="6">
-        <v>680.00120000000004</v>
+        <v>690.0018</v>
       </c>
       <c r="B274" s="6">
         <v>0</v>
@@ -5425,7 +5436,7 @@
     </row>
     <row r="275" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A275" s="6">
-        <v>690.0018</v>
+        <v>700.00149999999996</v>
       </c>
       <c r="B275" s="6">
         <v>0</v>
@@ -5445,7 +5456,7 @@
     </row>
     <row r="276" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A276" s="6">
-        <v>700.00149999999996</v>
+        <v>710.0018</v>
       </c>
       <c r="B276" s="6">
         <v>0</v>
@@ -5465,7 +5476,7 @@
     </row>
     <row r="277" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A277" s="6">
-        <v>710.0018</v>
+        <v>720.00149999999996</v>
       </c>
       <c r="B277" s="6">
         <v>0</v>
@@ -5485,7 +5496,7 @@
     </row>
     <row r="278" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A278" s="6">
-        <v>720.00149999999996</v>
+        <v>730.00149999999996</v>
       </c>
       <c r="B278" s="6">
         <v>0</v>
@@ -5505,7 +5516,7 @@
     </row>
     <row r="279" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A279" s="6">
-        <v>730.00149999999996</v>
+        <v>740.00239999999997</v>
       </c>
       <c r="B279" s="6">
         <v>0</v>
@@ -5525,7 +5536,7 @@
     </row>
     <row r="280" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A280" s="6">
-        <v>740.00239999999997</v>
+        <v>750.00239999999997</v>
       </c>
       <c r="B280" s="6">
         <v>0</v>
@@ -5545,7 +5556,7 @@
     </row>
     <row r="281" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A281" s="6">
-        <v>750.00239999999997</v>
+        <v>760.00199999999995</v>
       </c>
       <c r="B281" s="6">
         <v>0</v>
@@ -5565,7 +5576,7 @@
     </row>
     <row r="282" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A282" s="6">
-        <v>760.00199999999995</v>
+        <v>770.00210000000004</v>
       </c>
       <c r="B282" s="6">
         <v>0</v>
@@ -5585,7 +5596,7 @@
     </row>
     <row r="283" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A283" s="6">
-        <v>770.00210000000004</v>
+        <v>780.00160000000005</v>
       </c>
       <c r="B283" s="6">
         <v>0</v>
@@ -5605,7 +5616,7 @@
     </row>
     <row r="284" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A284" s="6">
-        <v>780.00160000000005</v>
+        <v>790.00160000000005</v>
       </c>
       <c r="B284" s="6">
         <v>0</v>
@@ -5625,7 +5636,7 @@
     </row>
     <row r="285" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A285" s="6">
-        <v>790.00160000000005</v>
+        <v>800.00210000000004</v>
       </c>
       <c r="B285" s="6">
         <v>0</v>
@@ -5645,7 +5656,7 @@
     </row>
     <row r="286" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A286" s="6">
-        <v>800.00210000000004</v>
+        <v>810.00239999999997</v>
       </c>
       <c r="B286" s="6">
         <v>0</v>
@@ -5665,7 +5676,7 @@
     </row>
     <row r="287" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A287" s="6">
-        <v>810.00239999999997</v>
+        <v>820.00170000000003</v>
       </c>
       <c r="B287" s="6">
         <v>0</v>
@@ -5685,7 +5696,7 @@
     </row>
     <row r="288" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A288" s="6">
-        <v>820.00170000000003</v>
+        <v>830.00170000000003</v>
       </c>
       <c r="B288" s="6">
         <v>0</v>
@@ -5705,7 +5716,7 @@
     </row>
     <row r="289" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A289" s="6">
-        <v>830.00170000000003</v>
+        <v>840.00199999999995</v>
       </c>
       <c r="B289" s="6">
         <v>0</v>
@@ -5725,7 +5736,7 @@
     </row>
     <row r="290" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A290" s="6">
-        <v>840.00199999999995</v>
+        <v>850.00170000000003</v>
       </c>
       <c r="B290" s="6">
         <v>0</v>
@@ -5745,7 +5756,7 @@
     </row>
     <row r="291" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A291" s="6">
-        <v>850.00170000000003</v>
+        <v>860.00220000000002</v>
       </c>
       <c r="B291" s="6">
         <v>0</v>
@@ -5765,7 +5776,7 @@
     </row>
     <row r="292" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A292" s="6">
-        <v>860.00220000000002</v>
+        <v>870.00220000000002</v>
       </c>
       <c r="B292" s="6">
         <v>0</v>
@@ -5785,7 +5796,7 @@
     </row>
     <row r="293" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A293" s="6">
-        <v>870.00220000000002</v>
+        <v>880.0027</v>
       </c>
       <c r="B293" s="6">
         <v>0</v>
@@ -5805,7 +5816,7 @@
     </row>
     <row r="294" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A294" s="6">
-        <v>880.0027</v>
+        <v>890.00139999999999</v>
       </c>
       <c r="B294" s="6">
         <v>0</v>
@@ -5825,7 +5836,7 @@
     </row>
     <row r="295" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A295" s="6">
-        <v>890.00139999999999</v>
+        <v>900.0018</v>
       </c>
       <c r="B295" s="6">
         <v>0</v>
@@ -5845,7 +5856,7 @@
     </row>
     <row r="296" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A296" s="6">
-        <v>900.0018</v>
+        <v>910.00210000000004</v>
       </c>
       <c r="B296" s="6">
         <v>0</v>
@@ -5865,7 +5876,7 @@
     </row>
     <row r="297" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A297" s="6">
-        <v>910.00210000000004</v>
+        <v>920.00139999999999</v>
       </c>
       <c r="B297" s="6">
         <v>0</v>
@@ -5885,7 +5896,7 @@
     </row>
     <row r="298" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A298" s="6">
-        <v>920.00139999999999</v>
+        <v>930.00199999999995</v>
       </c>
       <c r="B298" s="6">
         <v>0</v>
@@ -5905,7 +5916,7 @@
     </row>
     <row r="299" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A299" s="6">
-        <v>930.00199999999995</v>
+        <v>940.00160000000005</v>
       </c>
       <c r="B299" s="6">
         <v>0</v>
@@ -5925,7 +5936,7 @@
     </row>
     <row r="300" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A300" s="6">
-        <v>940.00160000000005</v>
+        <v>950.00130000000001</v>
       </c>
       <c r="B300" s="6">
         <v>0</v>
@@ -5945,7 +5956,7 @@
     </row>
     <row r="301" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A301" s="6">
-        <v>950.00130000000001</v>
+        <v>960.00210000000004</v>
       </c>
       <c r="B301" s="6">
         <v>0</v>
@@ -5965,7 +5976,7 @@
     </row>
     <row r="302" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A302" s="6">
-        <v>960.00210000000004</v>
+        <v>970.00120000000004</v>
       </c>
       <c r="B302" s="6">
         <v>0</v>
@@ -5985,7 +5996,7 @@
     </row>
     <row r="303" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A303" s="6">
-        <v>970.00120000000004</v>
+        <v>980.0018</v>
       </c>
       <c r="B303" s="6">
         <v>0</v>
@@ -6005,7 +6016,7 @@
     </row>
     <row r="304" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A304" s="6">
-        <v>980.0018</v>
+        <v>990.00220000000002</v>
       </c>
       <c r="B304" s="6">
         <v>0</v>
@@ -6025,7 +6036,7 @@
     </row>
     <row r="305" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
       <c r="A305" s="6">
-        <v>990.00220000000002</v>
+        <v>1000.002</v>
       </c>
       <c r="B305" s="6">
         <v>0</v>
@@ -6040,26 +6051,6 @@
         <v>0</v>
       </c>
       <c r="F305" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A306" s="6">
-        <v>1000.002</v>
-      </c>
-      <c r="B306" s="6">
-        <v>0</v>
-      </c>
-      <c r="C306" s="6">
-        <v>0</v>
-      </c>
-      <c r="D306" s="6">
-        <v>0</v>
-      </c>
-      <c r="E306" s="6">
-        <v>0</v>
-      </c>
-      <c r="F306" s="6">
         <v>0</v>
       </c>
     </row>
@@ -6083,7 +6074,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="36">
       <c r="A1" s="15" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6093,7 +6084,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="14" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -6103,692 +6094,692 @@
     </row>
     <row r="4" spans="1:6" ht="15">
       <c r="A4" s="13" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="8" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B5" s="8">
         <v>10000</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="8" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B6" s="8">
         <v>435.62599999999998</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="8" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B7" s="8">
         <v>2585.3270000000002</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="8" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B8" s="8">
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="8" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B9" s="8">
         <v>19</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="8" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B10" s="8">
         <v>50</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="8" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B11" s="8">
         <v>7800</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="8" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B12" s="8">
         <v>500</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B13" s="8">
         <v>1E-3</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="8" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B14" s="8">
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="8" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B15" s="8">
         <v>1.5</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="8" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B16" s="8">
         <v>2300</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="8" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B17" s="8">
         <v>900</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="8" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B18" s="8">
         <v>1.5</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="8" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B19" s="8">
         <v>517</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="8" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B20" s="8">
         <v>177</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="8" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="8" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B22" s="8">
         <v>1</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="8" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B23" s="8">
         <v>0</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B24" s="8">
         <v>15</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15">
       <c r="A26" s="12" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E26" s="12"/>
       <c r="F26" s="12"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="8" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B27" s="8">
         <v>101.325</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15">
       <c r="A28" s="10" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B28" s="10">
         <v>27</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B29" s="8">
         <v>27</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15">
       <c r="A30" s="10" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B30" s="10">
         <v>0.2</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
     </row>
     <row r="32" spans="1:6" ht="15">
       <c r="A32" s="10" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
     </row>
     <row r="33" spans="1:6" ht="15">
       <c r="A33" s="9" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B33" s="9">
         <v>86400</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" s="9" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B34" s="9">
         <v>2</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="8" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="8" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="8" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="8" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B38" s="8">
         <v>1</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="8" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B39" s="8">
         <v>575</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="8" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B41" s="8">
         <v>2738</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="8" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B42" s="8">
         <v>300</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15">
       <c r="A44" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E44" s="10"/>
       <c r="F44" s="10"/>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="8" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B45" s="11" t="b">
         <v>1</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="8" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B47" s="8">
         <v>0.8</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="8" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B48" s="8">
         <v>0</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B49" s="8">
         <v>0</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B50" s="8">
         <v>0</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="8" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B51" s="8">
         <v>0</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="8" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B52" s="8">
         <v>27</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15">
       <c r="A54" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B54" s="10">
         <v>500</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
     </row>
     <row r="55" spans="1:6" ht="15">
       <c r="A55" s="9" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E55" s="9"/>
       <c r="F55" s="9"/>
@@ -6804,7 +6795,7 @@
         <v>27</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -6818,12 +6809,12 @@
         <v>27</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15">
       <c r="A59" s="10" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B59" s="10"/>
       <c r="C59" s="10"/>
@@ -6833,13 +6824,13 @@
     </row>
     <row r="60" spans="1:6" ht="15">
       <c r="A60" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D60" s="9"/>
       <c r="E60" s="9"/>
@@ -6853,7 +6844,7 @@
         <v>0</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -6864,7 +6855,7 @@
         <v>0</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -6875,7 +6866,7 @@
         <v>5</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -6886,7 +6877,7 @@
         <v>5</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="15">
